--- a/Simulador_de_Investimentos.xlsx
+++ b/Simulador_de_Investimentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FC64D9-33F4-4F75-80FC-71797B1E9292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913F2138-A788-4C6D-AE86-9F8590288B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="653" xr2:uid="{2BDCCDF0-6679-4A66-BD97-5387F66B9F4F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="0" xr2:uid="{2BDCCDF0-6679-4A66-BD97-5387F66B9F4F}"/>
   </bookViews>
   <sheets>
     <sheet name="APP" sheetId="1" r:id="rId1"/>
@@ -164,9 +164,6 @@
     <t>Inflação Estimada (ao ano)</t>
   </si>
   <si>
-    <t>Descontos</t>
-  </si>
-  <si>
     <t>Imposto de Renda sobre o Lucro (20%)</t>
   </si>
   <si>
@@ -177,6 +174,9 @@
   </si>
   <si>
     <t>Poder de Compra Real</t>
+  </si>
+  <si>
+    <t>Análise de Retorno Real</t>
   </si>
 </sst>
 </file>
@@ -734,14 +734,38 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -749,37 +773,13 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1124,22 +1124,22 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.05</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.05</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1323,22 +1323,22 @@
                 <c:formatCode>"R$"\ #,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>126</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>630</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>252</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>126</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2392,80 +2392,80 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
     </row>
     <row r="3" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
       <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
     </row>
     <row r="7" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="56"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
     </row>
     <row r="9" spans="1:10" ht="33" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
     </row>
     <row r="10" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="55"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="3">
         <v>4200</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="51"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="4">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="49"/>
+      <c r="C12" s="45"/>
       <c r="D12" s="19">
         <f>D10*0.3</f>
         <v>1260</v>
@@ -2474,50 +2474,50 @@
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="55"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="5">
-        <v>1260</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="51"/>
+      <c r="C17" s="53"/>
       <c r="D17" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="51"/>
+      <c r="C18" s="53"/>
       <c r="D18" s="7">
-        <v>1.0789999999999999E-2</v>
+        <v>1.04E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8">
         <v>2</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="16">
         <f>FV(taxa_mensal, qtd_anos*12, Aporte*(-1))</f>
-        <v>306538.10778801696</v>
+        <v>165216.40555677837</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -2534,13 +2534,13 @@
       <c r="A21" s="8">
         <v>5</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="49"/>
+      <c r="C21" s="45"/>
       <c r="D21" s="19">
         <f>patrimonio*rendimento_carteira</f>
-        <v>1839.2286467281017</v>
+        <v>991.29843334067016</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -2560,10 +2560,10 @@
     </row>
     <row r="25" spans="1:4" ht="32.4" x14ac:dyDescent="0.4">
       <c r="A25" s="8"/>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="47"/>
       <c r="D25" s="9" t="s">
         <v>15</v>
       </c>
@@ -2575,11 +2575,11 @@
       </c>
       <c r="C26" s="12">
         <f>FV(taxa_mensal, $A19*12, Aporte*(-1))</f>
-        <v>34306.810395032975</v>
+        <v>13550.891352499742</v>
       </c>
       <c r="D26" s="13">
         <f>C26*rendimento_carteira</f>
-        <v>205.84086237019787</v>
+        <v>81.305348114998452</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="C27" s="15">
         <f>FV(taxa_mensal, $A21*12, Aporte*(-1))</f>
-        <v>105558.91163809443</v>
+        <v>41364.132868390334</v>
       </c>
       <c r="D27" s="16">
         <f>C27*rendimento_carteira</f>
-        <v>633.35346982856663</v>
+        <v>248.184797210342</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -2602,11 +2602,11 @@
       </c>
       <c r="C28" s="15">
         <f>FV(taxa_mensal, $A22*12, Aporte*(-1))</f>
-        <v>306538.10778801696</v>
+        <v>118316.88868622074</v>
       </c>
       <c r="D28" s="16">
         <f>C28*rendimento_carteira</f>
-        <v>1839.2286467281017</v>
+        <v>709.9013321173245</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.4">
@@ -2615,11 +2615,11 @@
       </c>
       <c r="C29" s="15">
         <f>FV(taxa_mensal, $A23*12, Aporte*(-1))</f>
-        <v>1417749.9841223215</v>
+        <v>527810.60925890261</v>
       </c>
       <c r="D29" s="16">
         <f>C29*rendimento_carteira</f>
-        <v>8506.4999047339297</v>
+        <v>3166.8636555534158</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2628,11 +2628,11 @@
       </c>
       <c r="C30" s="18">
         <f>FV(taxa_mensal, $A24*12, Aporte*(-1))</f>
-        <v>5445933.7653059401</v>
+        <v>1945064.8072894353</v>
       </c>
       <c r="D30" s="19">
         <f>C30*rendimento_carteira</f>
-        <v>32675.602591835643</v>
+        <v>11670.388843736611</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
@@ -2640,7 +2640,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D34" s="25"/>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C35" s="21">
         <f>Aporte</f>
-        <v>1260</v>
+        <v>500</v>
       </c>
       <c r="D35" s="22"/>
     </row>
@@ -2671,11 +2671,11 @@
       </c>
       <c r="C38" s="26">
         <f>VLOOKUP(perfil&amp;"-"&amp;B38, Planilha2!$A:$D,4, FALSE )</f>
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D38" s="32">
         <f>C38*$C$35</f>
-        <v>126</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.4">
@@ -2684,11 +2684,11 @@
       </c>
       <c r="C39" s="26">
         <f>VLOOKUP(perfil&amp;"-"&amp;B39, Planilha2!$A:$D,4, FALSE )</f>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D39" s="32">
         <f t="shared" ref="D39:D43" si="0">C39*$C$35</f>
-        <v>630</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
@@ -2697,11 +2697,11 @@
       </c>
       <c r="C40" s="26">
         <f>VLOOKUP(perfil&amp;"-"&amp;B40, Planilha2!$A:$D,4, FALSE )</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D40" s="32">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
@@ -2710,11 +2710,11 @@
       </c>
       <c r="C41" s="26">
         <f>VLOOKUP(perfil&amp;"-"&amp;B41, Planilha2!$A:$D,4, FALSE )</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="32">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
@@ -2723,11 +2723,11 @@
       </c>
       <c r="C42" s="26">
         <f>VLOOKUP(perfil&amp;"-"&amp;B42, Planilha2!$A:$D,4, FALSE )</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D42" s="32">
         <f t="shared" si="0"/>
-        <v>252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
@@ -2736,11 +2736,11 @@
       </c>
       <c r="C43" s="26">
         <f>VLOOKUP(perfil&amp;"-"&amp;B43, Planilha2!$A:$D,4, FALSE )</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="32">
         <f t="shared" si="0"/>
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
@@ -2748,59 +2748,64 @@
       <c r="C44" s="29"/>
       <c r="D44" s="30">
         <f>SUM(D38:D43)</f>
-        <v>1260</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" spans="2:4" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="60" spans="2:4" ht="32.4" x14ac:dyDescent="0.4">
-      <c r="B60" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C60" s="44"/>
-      <c r="D60" s="45"/>
+      <c r="B60" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" s="47"/>
+      <c r="D60" s="58"/>
     </row>
     <row r="61" spans="2:4" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="B61" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="C61" s="47"/>
+      <c r="B61" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="55"/>
       <c r="D61" s="16">
         <f>patrimonio-Aporte*qtd_anos*12</f>
-        <v>155338.10778801696</v>
+        <v>93216.405556778365</v>
       </c>
     </row>
     <row r="62" spans="2:4" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="B62" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" s="47"/>
+      <c r="B62" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C62" s="55"/>
       <c r="D62" s="16">
         <f>lucro_bruto*0.2</f>
-        <v>31067.621557603394</v>
+        <v>18643.281111355675</v>
       </c>
     </row>
     <row r="63" spans="2:4" ht="19.2" x14ac:dyDescent="0.4">
-      <c r="B63" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" s="47"/>
+      <c r="B63" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" s="55"/>
       <c r="D63" s="16">
         <f>lucro_bruto-imposto_renda</f>
-        <v>124270.48623041357</v>
+        <v>74573.124445422698</v>
       </c>
     </row>
     <row r="64" spans="2:4" ht="19.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B64" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" s="49"/>
+      <c r="B64" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="45"/>
       <c r="D64" s="19">
         <f>patrimonio_liquido/((1+inflacao)^qtd_anos)</f>
-        <v>80021.206143096628</v>
+        <v>43973.076775604044</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
     <mergeCell ref="A2:E7"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
@@ -2813,11 +2818,6 @@
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C34" xr:uid="{BE1BEE3C-B3AA-4AF4-9F56-C87964E5A309}">
